--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_mean_a_2019_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_mean_a_2019_magallanes.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 10:45</t>
+    <t xml:space="preserve">2026-10-01 23:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -506,7 +506,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="31.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="33.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_mean_a_2019_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_mean_a_2019_magallanes.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:15</t>
+    <t xml:space="preserve">2026-10-05 19:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
